--- a/data/STV_GLG.xlsx
+++ b/data/STV_GLG.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\haiyang\prediction\2026-浒苔消亡日期预测\moss_cover_prediction\STV-GLGFormer-area-only-2022-2024\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\AppData\Local\Temp\BvSshSftp-H7AM9KVM\BQ1F1698\QXK9K4CV\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="2022" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,13 +71,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -551,148 +544,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1899,7 +1892,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
